--- a/docs/workbook-split/dateien/Mehrjahresplan.xlsx
+++ b/docs/workbook-split/dateien/Mehrjahresplan.xlsx
@@ -651,25 +651,20 @@
           <t>Gesamtleistung</t>
         </is>
       </c>
-      <c r="D7" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C7)</f>
-        <v/>
+      <c r="D7" s="6" t="n">
+        <v>24480000</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>25704000</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>26989000</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>28338450</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>29755872.5</v>
       </c>
       <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="n"/>
@@ -687,25 +682,20 @@
           <t>Vorleistungen</t>
         </is>
       </c>
-      <c r="D8" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C8)</f>
-        <v/>
+      <c r="D8" s="6" t="n">
+        <v>15667400</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>15937230</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>16194960</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>16439889</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>16668743.5</v>
       </c>
       <c r="I8" s="1" t="n"/>
       <c r="J8" s="1" t="n"/>
@@ -723,25 +713,20 @@
           <t>Personalaufwand</t>
         </is>
       </c>
-      <c r="D9" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C9)</f>
-        <v/>
+      <c r="D9" s="6" t="n">
+        <v>5115000</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>5708537.73</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>6328127.029999999</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>6959583.260000001</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>7598231.39</v>
       </c>
       <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="n"/>
@@ -759,25 +744,20 @@
           <t>Raumkosten</t>
         </is>
       </c>
-      <c r="D10" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C10)</f>
-        <v/>
+      <c r="D10" s="6" t="n">
+        <v>243979.4</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>298858.99</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>304836.17</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>310932.8799999999</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>317151.54</v>
       </c>
       <c r="I10" s="1" t="n"/>
       <c r="J10" s="1" t="n"/>
@@ -795,25 +775,20 @@
           <t>Fuhrparkkosten</t>
         </is>
       </c>
-      <c r="D11" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C11)</f>
-        <v/>
+      <c r="D11" s="6" t="n">
+        <v>1573828.53</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1668258.24</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1768353.73</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1874454.96</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1986922.25</v>
       </c>
       <c r="I11" s="1" t="n"/>
       <c r="J11" s="1" t="n"/>
@@ -831,25 +806,20 @@
           <t>Instandh. Betriebsausstattung</t>
         </is>
       </c>
-      <c r="D12" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C12)</f>
-        <v/>
+      <c r="D12" s="6" t="n">
+        <v>51000</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>53550</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>56227.5</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>59038.88</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>61990.81</v>
       </c>
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
@@ -867,25 +837,20 @@
           <t>Vertriebskosten</t>
         </is>
       </c>
-      <c r="D13" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C13)</f>
-        <v/>
+      <c r="D13" s="6" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>136500</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>143325</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>150491.26</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>158015.82</v>
       </c>
       <c r="I13" s="1" t="n"/>
       <c r="J13" s="1" t="n"/>
@@ -903,25 +868,20 @@
           <t>Verwaltungskosten</t>
         </is>
       </c>
-      <c r="D14" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2027,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2028,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2029,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2030,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)+SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,2031,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,$C14)</f>
-        <v/>
+      <c r="D14" s="6" t="n">
+        <v>705000</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>726150</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>747934.5</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>770372.53</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>793483.7000000001</v>
       </c>
       <c r="I14" s="1" t="n"/>
       <c r="J14" s="1" t="n"/>
@@ -956,25 +916,20 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="D16" s="9">
-        <f>D7-SUM(D8:D14)</f>
-        <v/>
-      </c>
-      <c r="E16" s="9">
-        <f>E7-SUM(E8:E14)</f>
-        <v/>
-      </c>
-      <c r="F16" s="9">
-        <f>F7-SUM(F8:F14)</f>
-        <v/>
-      </c>
-      <c r="G16" s="9">
-        <f>G7-SUM(G8:G14)</f>
-        <v/>
-      </c>
-      <c r="H16" s="9">
-        <f>H7-SUM(H8:H14)</f>
-        <v/>
+      <c r="D16" s="9" t="n">
+        <v>993792.0700000003</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>1174915.040000003</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>1445236.069999997</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>1773687.229999997</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>2171333.490000002</v>
       </c>
       <c r="I16" s="1" t="n"/>
       <c r="J16" s="1" t="n"/>
@@ -992,25 +947,20 @@
           <t>EBITDA-Marge</t>
         </is>
       </c>
-      <c r="D17" s="10">
-        <f>IF(D7=0,"n.a.",D16/D7)</f>
-        <v/>
-      </c>
-      <c r="E17" s="10">
-        <f>IF(E7=0,"n.a.",E16/E7)</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
-        <f>IF(F7=0,"n.a.",F16/F7)</f>
-        <v/>
-      </c>
-      <c r="G17" s="10">
-        <f>IF(G7=0,"n.a.",G16/G7)</f>
-        <v/>
-      </c>
-      <c r="H17" s="10">
-        <f>IF(H7=0,"n.a.",H16/H7)</f>
-        <v/>
+      <c r="D17" s="10" t="n">
+        <v>0.04059608129084968</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.04570942421413021</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0.053549078142947</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>0.06258942285128498</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>0.07297159543885</v>
       </c>
       <c r="I17" s="1" t="n"/>
       <c r="J17" s="1" t="n"/>
@@ -1146,21 +1096,17 @@
           <t>West</t>
         </is>
       </c>
-      <c r="D24" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="E24" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="F24" s="7">
-        <f>D24-E24</f>
-        <v/>
-      </c>
-      <c r="G24" s="10">
-        <f>IF(D24=0,"n.a.",F24/D24)</f>
-        <v/>
+      <c r="D24" s="6" t="n">
+        <v>13880000</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>12217454.01</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>1662545.99</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>0.1197799704610951</v>
       </c>
       <c r="H24" s="1" t="n"/>
       <c r="I24" s="1" t="n"/>
@@ -1179,21 +1125,17 @@
           <t>Süd-West</t>
         </is>
       </c>
-      <c r="D25" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="E25" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="F25" s="7">
-        <f>D25-E25</f>
-        <v/>
-      </c>
-      <c r="G25" s="10">
-        <f>IF(D25=0,"n.a.",F25/D25)</f>
-        <v/>
+      <c r="D25" s="6" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>4376888.56</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>423111.4400000004</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>0.08814821666666675</v>
       </c>
       <c r="H25" s="1" t="n"/>
       <c r="I25" s="1" t="n"/>
@@ -1212,21 +1154,17 @@
           <t>Ost</t>
         </is>
       </c>
-      <c r="D26" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="E26" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="F26" s="7">
-        <f>D26-E26</f>
-        <v/>
-      </c>
-      <c r="G26" s="10">
-        <f>IF(D26=0,"n.a.",F26/D26)</f>
-        <v/>
+      <c r="D26" s="6" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>4072125.78</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>227874.2200000002</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0.05299400465116284</v>
       </c>
       <c r="H26" s="1" t="n"/>
       <c r="I26" s="1" t="n"/>
@@ -1245,21 +1183,17 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D27" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="E27" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="F27" s="7">
-        <f>D27-E27</f>
-        <v/>
-      </c>
-      <c r="G27" s="10">
-        <f>IF(D27=0,"n.a.",F27/D27)</f>
-        <v/>
+      <c r="D27" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1460582.05</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>39417.94999999995</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0.0262786333333333</v>
       </c>
       <c r="H27" s="1" t="n"/>
       <c r="I27" s="1" t="n"/>
@@ -1278,21 +1212,19 @@
           <t>Verwaltung</t>
         </is>
       </c>
-      <c r="D28" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="E28" s="6">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="F28" s="7">
-        <f>D28-E28</f>
-        <v/>
-      </c>
-      <c r="G28" s="10">
-        <f>IF(D28=0,"n.a.",F28/D28)</f>
-        <v/>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>1359157.53</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>-1359157.53</v>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="H28" s="1" t="n"/>
       <c r="I28" s="1" t="n"/>
@@ -1847,6 +1779,8 @@
       <c r="N60" s="1" t="n"/>
       <c r="O60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
